--- a/data/source_data/Supplementary_TableS2_Figure4_LME.xlsx
+++ b/data/source_data/Supplementary_TableS2_Figure4_LME.xlsx
@@ -2,15 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MATLABコード\小論文用\Figure\SourceData_Workbooks\書き換えた論文の番号対応ソース\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9C1A8D2-3C80-4161-868F-1A38FB08B644}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{069D7098-AEFD-497B-BFD4-12C896BBEC65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2268" yWindow="2268" windowWidth="17280" windowHeight="8820" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-22140" yWindow="-8610" windowWidth="21600" windowHeight="11235" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -330,7 +325,7 @@
   <numFmts count="3">
     <numFmt numFmtId="176" formatCode="0.0000"/>
     <numFmt numFmtId="177" formatCode="0.000"/>
-    <numFmt numFmtId="194" formatCode="0.0.E+00"/>
+    <numFmt numFmtId="178" formatCode="0.0.E+00"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -426,8 +421,8 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="194" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -438,7 +433,7 @@
   </cellStyles>
   <dxfs count="1">
     <dxf>
-      <numFmt numFmtId="194" formatCode="0.0.E+00"/>
+      <numFmt numFmtId="178" formatCode="0.0.E+00"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
